--- a/backend/wp_templates/H/H5 油气资产.xlsx
+++ b/backend/wp_templates/H/H5 油气资产.xlsx
@@ -34268,58 +34268,6 @@
   </headerFooter>
   <drawing r:id="rId2"/>
   <legacyDrawing r:id="rId3"/>
-  <oleObjects>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice Requires="x14">
-        <oleObject progId="Equation.3" shapeId="5121" r:id="rId4">
-          <objectPr defaultSize="0" autoPict="0" r:id="rId5">
-            <anchor moveWithCells="1" sizeWithCells="1">
-              <from>
-                <xdr:col>0</xdr:col>
-                <xdr:colOff>99060</xdr:colOff>
-                <xdr:row>51</xdr:row>
-                <xdr:rowOff>45720</xdr:rowOff>
-              </from>
-              <to>
-                <xdr:col>3</xdr:col>
-                <xdr:colOff>0</xdr:colOff>
-                <xdr:row>53</xdr:row>
-                <xdr:rowOff>137160</xdr:rowOff>
-              </to>
-            </anchor>
-          </objectPr>
-        </oleObject>
-      </mc:Choice>
-      <mc:Fallback>
-        <oleObject progId="Equation.3" shapeId="5121" r:id="rId4"/>
-      </mc:Fallback>
-    </mc:AlternateContent>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice Requires="x14">
-        <oleObject progId="Equation.3" shapeId="5122" r:id="rId6">
-          <objectPr defaultSize="0" autoPict="0" r:id="rId7">
-            <anchor moveWithCells="1" sizeWithCells="1">
-              <from>
-                <xdr:col>3</xdr:col>
-                <xdr:colOff>655320</xdr:colOff>
-                <xdr:row>51</xdr:row>
-                <xdr:rowOff>144780</xdr:rowOff>
-              </from>
-              <to>
-                <xdr:col>7</xdr:col>
-                <xdr:colOff>198120</xdr:colOff>
-                <xdr:row>53</xdr:row>
-                <xdr:rowOff>76200</xdr:rowOff>
-              </to>
-            </anchor>
-          </objectPr>
-        </oleObject>
-      </mc:Choice>
-      <mc:Fallback>
-        <oleObject progId="Equation.3" shapeId="5122" r:id="rId6"/>
-      </mc:Fallback>
-    </mc:AlternateContent>
-  </oleObjects>
 </worksheet>
 </file>
 
